--- a/artfynd/A 1933-2022 artfynd.xlsx
+++ b/artfynd/A 1933-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1933-2022 artfynd.xlsx
+++ b/artfynd/A 1933-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>98240492</v>
       </c>
       <c r="B2" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565271.646136292</v>
+        <v>565272</v>
       </c>
       <c r="R2" t="n">
-        <v>6269141.752300831</v>
+        <v>6269142</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-01-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-01-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98240541</v>
+        <v>98240490</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -843,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565540.0605983417</v>
+        <v>565168</v>
       </c>
       <c r="R3" t="n">
-        <v>6269138.7492882</v>
+        <v>6269185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,19 +856,9 @@
           <t>2022-01-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-01-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98240552</v>
+        <v>98240541</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,7 +916,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565557.5554716657</v>
+        <v>565540</v>
       </c>
       <c r="R4" t="n">
-        <v>6269150.042478747</v>
+        <v>6269139</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,19 +966,9 @@
           <t>2022-01-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-01-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,42 +996,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98244107</v>
+        <v>98240544</v>
       </c>
       <c r="B5" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565603.796491991</v>
+        <v>565552</v>
       </c>
       <c r="R5" t="n">
-        <v>6269123.758733781</v>
+        <v>6269146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,19 +1076,9 @@
           <t>2022-01-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-01-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,15 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98240560</v>
+        <v>98240552</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1209,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565556.6567886991</v>
+        <v>565558</v>
       </c>
       <c r="R6" t="n">
-        <v>6269136.802835705</v>
+        <v>6269150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,19 +1186,9 @@
           <t>2022-01-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-01-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,15 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98240565</v>
+        <v>98240560</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1246,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1334,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565566.0590209593</v>
+        <v>565557</v>
       </c>
       <c r="R7" t="n">
-        <v>6269135.846791171</v>
+        <v>6269137</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,19 +1296,9 @@
           <t>2022-01-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-01-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,15 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98240544</v>
+        <v>98240565</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1356,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1459,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565551.5426893543</v>
+        <v>565566</v>
       </c>
       <c r="R8" t="n">
-        <v>6269146.091572395</v>
+        <v>6269136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,19 +1406,9 @@
           <t>2022-01-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-01-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,6 +1433,107 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>98244107</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92348</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skällby 5:4, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>565604</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6269124</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1933-2022 artfynd.xlsx
+++ b/artfynd/A 1933-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98240492</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98244107</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98240490</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98240541</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98240544</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98240552</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98240560</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,8 +1574,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98240565</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>